--- a/api/請求書テンプレ.xlsx
+++ b/api/請求書テンプレ.xlsx
@@ -157,7 +157,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -530,6 +530,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
@@ -542,7 +568,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -716,6 +742,21 @@
     </xf>
     <xf numFmtId="3" fontId="11" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1437,23 +1478,23 @@
           <t>数量</t>
         </is>
       </c>
-      <c r="R16" s="57" t="inlineStr">
+      <c r="R16" s="68" t="inlineStr">
         <is>
           <t>単位</t>
         </is>
       </c>
-      <c r="S16" s="57" t="inlineStr">
+      <c r="S16" s="68" t="inlineStr">
         <is>
           <t>単価</t>
         </is>
       </c>
-      <c r="T16" s="57" t="inlineStr">
+      <c r="T16" s="61" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
       </c>
       <c r="U16" s="34" t="n"/>
-      <c r="V16" s="35" t="n"/>
+      <c r="V16" s="45" t="n"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" s="50">
       <c r="A17" s="22" t="inlineStr">
@@ -1480,14 +1521,14 @@
       <c r="O17" s="19" t="n"/>
       <c r="P17" s="53" t="n"/>
       <c r="Q17" s="8" t="n"/>
-      <c r="R17" s="63" t="n"/>
-      <c r="S17" s="64" t="n"/>
-      <c r="T17" s="58">
+      <c r="R17" s="69" t="n"/>
+      <c r="S17" s="70" t="n"/>
+      <c r="T17" s="62">
         <f>S17*Q17</f>
         <v/>
       </c>
       <c r="U17" s="18" t="n"/>
-      <c r="V17" s="19" t="n"/>
+      <c r="V17" s="26" t="n"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" s="50">
       <c r="A18" s="22" t="n"/>
@@ -1510,14 +1551,14 @@
       <c r="O18" s="19" t="n"/>
       <c r="P18" s="53" t="n"/>
       <c r="Q18" s="8" t="n"/>
-      <c r="R18" s="63" t="n"/>
-      <c r="S18" s="64" t="n"/>
-      <c r="T18" s="58">
+      <c r="R18" s="69" t="n"/>
+      <c r="S18" s="70" t="n"/>
+      <c r="T18" s="62">
         <f>S18*Q18</f>
         <v/>
       </c>
       <c r="U18" s="18" t="n"/>
-      <c r="V18" s="19" t="n"/>
+      <c r="V18" s="26" t="n"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" s="50">
       <c r="A19" s="22" t="n"/>
@@ -1540,14 +1581,14 @@
       <c r="O19" s="19" t="n"/>
       <c r="P19" s="53" t="n"/>
       <c r="Q19" s="8" t="n"/>
-      <c r="R19" s="63" t="n"/>
-      <c r="S19" s="64" t="n"/>
-      <c r="T19" s="58">
+      <c r="R19" s="69" t="n"/>
+      <c r="S19" s="70" t="n"/>
+      <c r="T19" s="62">
         <f>S19*Q19</f>
         <v/>
       </c>
       <c r="U19" s="18" t="n"/>
-      <c r="V19" s="19" t="n"/>
+      <c r="V19" s="26" t="n"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" s="50">
       <c r="A20" s="22" t="n"/>
@@ -1570,14 +1611,14 @@
       <c r="O20" s="19" t="n"/>
       <c r="P20" s="53" t="n"/>
       <c r="Q20" s="8" t="n"/>
-      <c r="R20" s="63" t="n"/>
-      <c r="S20" s="64" t="n"/>
-      <c r="T20" s="58">
+      <c r="R20" s="69" t="n"/>
+      <c r="S20" s="70" t="n"/>
+      <c r="T20" s="62">
         <f>S20*Q20</f>
         <v/>
       </c>
       <c r="U20" s="18" t="n"/>
-      <c r="V20" s="19" t="n"/>
+      <c r="V20" s="26" t="n"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" s="50">
       <c r="A21" s="22" t="n"/>
@@ -1600,14 +1641,14 @@
       <c r="O21" s="19" t="n"/>
       <c r="P21" s="53" t="n"/>
       <c r="Q21" s="8" t="n"/>
-      <c r="R21" s="63" t="n"/>
-      <c r="S21" s="64" t="n"/>
-      <c r="T21" s="58">
+      <c r="R21" s="69" t="n"/>
+      <c r="S21" s="70" t="n"/>
+      <c r="T21" s="62">
         <f>S21*Q21</f>
         <v/>
       </c>
       <c r="U21" s="18" t="n"/>
-      <c r="V21" s="19" t="n"/>
+      <c r="V21" s="26" t="n"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" s="50">
       <c r="A22" s="22" t="n"/>
@@ -1630,14 +1671,14 @@
       <c r="O22" s="19" t="n"/>
       <c r="P22" s="53" t="n"/>
       <c r="Q22" s="8" t="n"/>
-      <c r="R22" s="63" t="n"/>
-      <c r="S22" s="64" t="n"/>
-      <c r="T22" s="58">
+      <c r="R22" s="69" t="n"/>
+      <c r="S22" s="70" t="n"/>
+      <c r="T22" s="62">
         <f>S22*Q22</f>
         <v/>
       </c>
       <c r="U22" s="18" t="n"/>
-      <c r="V22" s="19" t="n"/>
+      <c r="V22" s="26" t="n"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" s="50">
       <c r="A23" s="22" t="n"/>
@@ -1660,14 +1701,14 @@
       <c r="O23" s="19" t="n"/>
       <c r="P23" s="53" t="n"/>
       <c r="Q23" s="8" t="n"/>
-      <c r="R23" s="63" t="n"/>
-      <c r="S23" s="64" t="n"/>
-      <c r="T23" s="58">
+      <c r="R23" s="69" t="n"/>
+      <c r="S23" s="70" t="n"/>
+      <c r="T23" s="62">
         <f>S23*Q23</f>
         <v/>
       </c>
       <c r="U23" s="18" t="n"/>
-      <c r="V23" s="19" t="n"/>
+      <c r="V23" s="26" t="n"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" s="50">
       <c r="A24" s="22" t="n"/>
@@ -1690,14 +1731,14 @@
       <c r="O24" s="19" t="n"/>
       <c r="P24" s="53" t="n"/>
       <c r="Q24" s="8" t="n"/>
-      <c r="R24" s="63" t="n"/>
-      <c r="S24" s="64" t="n"/>
-      <c r="T24" s="58">
+      <c r="R24" s="69" t="n"/>
+      <c r="S24" s="70" t="n"/>
+      <c r="T24" s="62">
         <f>S24*Q24</f>
         <v/>
       </c>
       <c r="U24" s="18" t="n"/>
-      <c r="V24" s="19" t="n"/>
+      <c r="V24" s="26" t="n"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" s="50">
       <c r="A25" s="22" t="n"/>
@@ -1720,14 +1761,14 @@
       <c r="O25" s="19" t="n"/>
       <c r="P25" s="53" t="n"/>
       <c r="Q25" s="8" t="n"/>
-      <c r="R25" s="63" t="n"/>
-      <c r="S25" s="64" t="n"/>
-      <c r="T25" s="58">
+      <c r="R25" s="69" t="n"/>
+      <c r="S25" s="70" t="n"/>
+      <c r="T25" s="62">
         <f>S25*Q25</f>
         <v/>
       </c>
       <c r="U25" s="18" t="n"/>
-      <c r="V25" s="19" t="n"/>
+      <c r="V25" s="26" t="n"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" s="50">
       <c r="A26" s="22" t="n"/>
@@ -1750,14 +1791,14 @@
       <c r="O26" s="19" t="n"/>
       <c r="P26" s="53" t="n"/>
       <c r="Q26" s="8" t="n"/>
-      <c r="R26" s="63" t="n"/>
-      <c r="S26" s="64" t="n"/>
-      <c r="T26" s="58">
+      <c r="R26" s="69" t="n"/>
+      <c r="S26" s="70" t="n"/>
+      <c r="T26" s="62">
         <f>S26*Q26</f>
         <v/>
       </c>
       <c r="U26" s="18" t="n"/>
-      <c r="V26" s="19" t="n"/>
+      <c r="V26" s="26" t="n"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" s="50">
       <c r="A27" s="22" t="n"/>
@@ -1780,14 +1821,14 @@
       <c r="O27" s="19" t="n"/>
       <c r="P27" s="53" t="n"/>
       <c r="Q27" s="8" t="n"/>
-      <c r="R27" s="63" t="n"/>
-      <c r="S27" s="64" t="n"/>
-      <c r="T27" s="58">
+      <c r="R27" s="69" t="n"/>
+      <c r="S27" s="70" t="n"/>
+      <c r="T27" s="62">
         <f>S27*Q27</f>
         <v/>
       </c>
       <c r="U27" s="18" t="n"/>
-      <c r="V27" s="19" t="n"/>
+      <c r="V27" s="26" t="n"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" s="50">
       <c r="A28" s="22" t="n"/>
@@ -1810,14 +1851,14 @@
       <c r="O28" s="19" t="n"/>
       <c r="P28" s="53" t="n"/>
       <c r="Q28" s="8" t="n"/>
-      <c r="R28" s="63" t="n"/>
-      <c r="S28" s="64" t="n"/>
-      <c r="T28" s="58">
+      <c r="R28" s="69" t="n"/>
+      <c r="S28" s="70" t="n"/>
+      <c r="T28" s="62">
         <f>S28*Q28</f>
         <v/>
       </c>
       <c r="U28" s="18" t="n"/>
-      <c r="V28" s="19" t="n"/>
+      <c r="V28" s="26" t="n"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" s="50">
       <c r="A29" s="22" t="n"/>
@@ -1840,14 +1881,14 @@
       <c r="O29" s="19" t="n"/>
       <c r="P29" s="53" t="n"/>
       <c r="Q29" s="8" t="n"/>
-      <c r="R29" s="63" t="n"/>
-      <c r="S29" s="65" t="n"/>
-      <c r="T29" s="58">
+      <c r="R29" s="69" t="n"/>
+      <c r="S29" s="71" t="n"/>
+      <c r="T29" s="62">
         <f>S29*Q29</f>
         <v/>
       </c>
       <c r="U29" s="18" t="n"/>
-      <c r="V29" s="19" t="n"/>
+      <c r="V29" s="26" t="n"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" s="50">
       <c r="A30" s="22" t="n"/>
@@ -1870,14 +1911,14 @@
       <c r="O30" s="19" t="n"/>
       <c r="P30" s="55" t="n"/>
       <c r="Q30" s="11" t="n"/>
-      <c r="R30" s="66" t="n"/>
-      <c r="S30" s="65" t="n"/>
-      <c r="T30" s="58">
+      <c r="R30" s="72" t="n"/>
+      <c r="S30" s="71" t="n"/>
+      <c r="T30" s="62">
         <f>S30*Q30</f>
         <v/>
       </c>
       <c r="U30" s="18" t="n"/>
-      <c r="V30" s="19" t="n"/>
+      <c r="V30" s="26" t="n"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" s="50">
       <c r="A31" s="22" t="n"/>
@@ -1900,14 +1941,14 @@
       <c r="O31" s="19" t="n"/>
       <c r="P31" s="55" t="n"/>
       <c r="Q31" s="11" t="n"/>
-      <c r="R31" s="66" t="n"/>
-      <c r="S31" s="65" t="n"/>
-      <c r="T31" s="58">
+      <c r="R31" s="72" t="n"/>
+      <c r="S31" s="71" t="n"/>
+      <c r="T31" s="62">
         <f>S31*Q31</f>
         <v/>
       </c>
       <c r="U31" s="18" t="n"/>
-      <c r="V31" s="19" t="n"/>
+      <c r="V31" s="26" t="n"/>
     </row>
     <row r="32" ht="20.1" customHeight="1" s="50">
       <c r="A32" s="47" t="n"/>
@@ -1930,14 +1971,14 @@
       <c r="O32" s="19" t="n"/>
       <c r="P32" s="55" t="n"/>
       <c r="Q32" s="11" t="n"/>
-      <c r="R32" s="66" t="n"/>
-      <c r="S32" s="66" t="n"/>
-      <c r="T32" s="58">
+      <c r="R32" s="72" t="n"/>
+      <c r="S32" s="72" t="n"/>
+      <c r="T32" s="62">
         <f>S32*Q32</f>
         <v/>
       </c>
       <c r="U32" s="18" t="n"/>
-      <c r="V32" s="19" t="n"/>
+      <c r="V32" s="26" t="n"/>
     </row>
     <row r="33" ht="20.1" customHeight="1" s="50">
       <c r="A33" s="36" t="inlineStr">
@@ -1964,14 +2005,14 @@
       <c r="O33" s="19" t="n"/>
       <c r="P33" s="55" t="n"/>
       <c r="Q33" s="11" t="n"/>
-      <c r="R33" s="66" t="n"/>
-      <c r="S33" s="65" t="n"/>
-      <c r="T33" s="58">
+      <c r="R33" s="72" t="n"/>
+      <c r="S33" s="71" t="n"/>
+      <c r="T33" s="62">
         <f>S33*Q33</f>
         <v/>
       </c>
       <c r="U33" s="18" t="n"/>
-      <c r="V33" s="19" t="n"/>
+      <c r="V33" s="26" t="n"/>
     </row>
     <row r="34" ht="20.1" customHeight="1" s="50">
       <c r="A34" s="36" t="inlineStr">
@@ -1998,14 +2039,14 @@
       <c r="O34" s="19" t="n"/>
       <c r="P34" s="55" t="n"/>
       <c r="Q34" s="11" t="n"/>
-      <c r="R34" s="66" t="n"/>
-      <c r="S34" s="66" t="n"/>
-      <c r="T34" s="58">
+      <c r="R34" s="72" t="n"/>
+      <c r="S34" s="72" t="n"/>
+      <c r="T34" s="62">
         <f>S34*Q34</f>
         <v/>
       </c>
       <c r="U34" s="18" t="n"/>
-      <c r="V34" s="19" t="n"/>
+      <c r="V34" s="26" t="n"/>
     </row>
     <row r="35" ht="20.1" customHeight="1" s="50" thickBot="1">
       <c r="A35" s="38" t="inlineStr">
@@ -2038,12 +2079,12 @@
       <c r="Q35" s="18" t="n"/>
       <c r="R35" s="18" t="n"/>
       <c r="S35" s="19" t="n"/>
-      <c r="T35" s="58">
+      <c r="T35" s="62">
         <f>SUM(T17:V34)</f>
         <v/>
       </c>
       <c r="U35" s="18" t="n"/>
-      <c r="V35" s="19" t="n"/>
+      <c r="V35" s="26" t="n"/>
     </row>
     <row r="36" ht="20.1" customHeight="1" s="50">
       <c r="A36" s="49" t="inlineStr">
@@ -2063,12 +2104,12 @@
       <c r="Q36" s="18" t="n"/>
       <c r="R36" s="18" t="n"/>
       <c r="S36" s="19" t="n"/>
-      <c r="T36" s="59">
+      <c r="T36" s="67">
         <f>T35*10%</f>
         <v/>
       </c>
       <c r="U36" s="18" t="n"/>
-      <c r="V36" s="19" t="n"/>
+      <c r="V36" s="26" t="n"/>
     </row>
     <row r="37" ht="20.1" customHeight="1" s="50" thickBot="1">
       <c r="L37" s="38" t="inlineStr">
@@ -2083,7 +2124,7 @@
       <c r="Q37" s="30" t="n"/>
       <c r="R37" s="30" t="n"/>
       <c r="S37" s="39" t="n"/>
-      <c r="T37" s="60">
+      <c r="T37" s="29">
         <f>T35+T36</f>
         <v/>
       </c>
@@ -3256,13 +3297,13 @@
           <t>単価</t>
         </is>
       </c>
-      <c r="I16" s="57" t="inlineStr">
+      <c r="I16" s="61" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
       </c>
       <c r="J16" s="34" t="n"/>
-      <c r="K16" s="35" t="n"/>
+      <c r="K16" s="45" t="n"/>
       <c r="L16" s="33" t="inlineStr">
         <is>
           <t>品名・内容</t>
@@ -3281,23 +3322,23 @@
           <t>数量</t>
         </is>
       </c>
-      <c r="R16" s="57" t="inlineStr">
+      <c r="R16" s="68" t="inlineStr">
         <is>
           <t>単位</t>
         </is>
       </c>
-      <c r="S16" s="57" t="inlineStr">
+      <c r="S16" s="68" t="inlineStr">
         <is>
           <t>単価</t>
         </is>
       </c>
-      <c r="T16" s="57" t="inlineStr">
+      <c r="T16" s="61" t="inlineStr">
         <is>
           <t>金額</t>
         </is>
       </c>
       <c r="U16" s="34" t="n"/>
-      <c r="V16" s="35" t="n"/>
+      <c r="V16" s="45" t="n"/>
     </row>
     <row r="17" ht="20.1" customHeight="1" s="50">
       <c r="A17" s="22" t="inlineStr">
@@ -3312,26 +3353,26 @@
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
       <c r="H17" s="9" t="n"/>
-      <c r="I17" s="58">
+      <c r="I17" s="62">
         <f>T35</f>
         <v/>
       </c>
       <c r="J17" s="18" t="n"/>
-      <c r="K17" s="19" t="n"/>
+      <c r="K17" s="26" t="n"/>
       <c r="L17" s="22" t="n"/>
       <c r="M17" s="18" t="n"/>
       <c r="N17" s="18" t="n"/>
       <c r="O17" s="19" t="n"/>
       <c r="P17" s="53" t="n"/>
       <c r="Q17" s="8" t="n"/>
-      <c r="R17" s="63" t="n"/>
-      <c r="S17" s="64" t="n"/>
-      <c r="T17" s="58">
+      <c r="R17" s="69" t="n"/>
+      <c r="S17" s="70" t="n"/>
+      <c r="T17" s="62">
         <f>S17*Q17</f>
         <v/>
       </c>
       <c r="U17" s="18" t="n"/>
-      <c r="V17" s="19" t="n"/>
+      <c r="V17" s="26" t="n"/>
     </row>
     <row r="18" ht="20.1" customHeight="1" s="50">
       <c r="A18" s="22" t="n"/>
@@ -3342,26 +3383,26 @@
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
       <c r="H18" s="9" t="n"/>
-      <c r="I18" s="58">
+      <c r="I18" s="62">
         <f>H18*F18</f>
         <v/>
       </c>
       <c r="J18" s="18" t="n"/>
-      <c r="K18" s="19" t="n"/>
+      <c r="K18" s="26" t="n"/>
       <c r="L18" s="22" t="n"/>
       <c r="M18" s="18" t="n"/>
       <c r="N18" s="18" t="n"/>
       <c r="O18" s="19" t="n"/>
       <c r="P18" s="53" t="n"/>
       <c r="Q18" s="8" t="n"/>
-      <c r="R18" s="63" t="n"/>
-      <c r="S18" s="64" t="n"/>
-      <c r="T18" s="58">
+      <c r="R18" s="69" t="n"/>
+      <c r="S18" s="70" t="n"/>
+      <c r="T18" s="62">
         <f>S18*Q18</f>
         <v/>
       </c>
       <c r="U18" s="18" t="n"/>
-      <c r="V18" s="19" t="n"/>
+      <c r="V18" s="26" t="n"/>
     </row>
     <row r="19" ht="20.1" customHeight="1" s="50">
       <c r="A19" s="22" t="n"/>
@@ -3372,26 +3413,26 @@
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="9" t="n"/>
-      <c r="I19" s="58">
+      <c r="I19" s="62">
         <f>H19*F19</f>
         <v/>
       </c>
       <c r="J19" s="18" t="n"/>
-      <c r="K19" s="19" t="n"/>
+      <c r="K19" s="26" t="n"/>
       <c r="L19" s="22" t="n"/>
       <c r="M19" s="18" t="n"/>
       <c r="N19" s="18" t="n"/>
       <c r="O19" s="19" t="n"/>
       <c r="P19" s="53" t="n"/>
       <c r="Q19" s="8" t="n"/>
-      <c r="R19" s="63" t="n"/>
-      <c r="S19" s="64" t="n"/>
-      <c r="T19" s="58">
+      <c r="R19" s="69" t="n"/>
+      <c r="S19" s="70" t="n"/>
+      <c r="T19" s="62">
         <f>S19*Q19</f>
         <v/>
       </c>
       <c r="U19" s="18" t="n"/>
-      <c r="V19" s="19" t="n"/>
+      <c r="V19" s="26" t="n"/>
     </row>
     <row r="20" ht="20.1" customHeight="1" s="50">
       <c r="A20" s="22" t="n"/>
@@ -3402,26 +3443,26 @@
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="9" t="n"/>
-      <c r="I20" s="58">
+      <c r="I20" s="62">
         <f>H20*F20</f>
         <v/>
       </c>
       <c r="J20" s="18" t="n"/>
-      <c r="K20" s="19" t="n"/>
+      <c r="K20" s="26" t="n"/>
       <c r="L20" s="22" t="n"/>
       <c r="M20" s="18" t="n"/>
       <c r="N20" s="18" t="n"/>
       <c r="O20" s="19" t="n"/>
       <c r="P20" s="53" t="n"/>
       <c r="Q20" s="8" t="n"/>
-      <c r="R20" s="63" t="n"/>
-      <c r="S20" s="64" t="n"/>
-      <c r="T20" s="58">
+      <c r="R20" s="69" t="n"/>
+      <c r="S20" s="70" t="n"/>
+      <c r="T20" s="62">
         <f>S20*Q20</f>
         <v/>
       </c>
       <c r="U20" s="18" t="n"/>
-      <c r="V20" s="19" t="n"/>
+      <c r="V20" s="26" t="n"/>
     </row>
     <row r="21" ht="20.1" customHeight="1" s="50">
       <c r="A21" s="22" t="n"/>
@@ -3432,26 +3473,26 @@
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="9" t="n"/>
-      <c r="I21" s="58">
+      <c r="I21" s="62">
         <f>H21*F21</f>
         <v/>
       </c>
       <c r="J21" s="18" t="n"/>
-      <c r="K21" s="19" t="n"/>
+      <c r="K21" s="26" t="n"/>
       <c r="L21" s="22" t="n"/>
       <c r="M21" s="18" t="n"/>
       <c r="N21" s="18" t="n"/>
       <c r="O21" s="19" t="n"/>
       <c r="P21" s="53" t="n"/>
       <c r="Q21" s="8" t="n"/>
-      <c r="R21" s="63" t="n"/>
-      <c r="S21" s="64" t="n"/>
-      <c r="T21" s="58">
+      <c r="R21" s="69" t="n"/>
+      <c r="S21" s="70" t="n"/>
+      <c r="T21" s="62">
         <f>S21*Q21</f>
         <v/>
       </c>
       <c r="U21" s="18" t="n"/>
-      <c r="V21" s="19" t="n"/>
+      <c r="V21" s="26" t="n"/>
     </row>
     <row r="22" ht="20.1" customHeight="1" s="50">
       <c r="A22" s="22" t="n"/>
@@ -3462,26 +3503,26 @@
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="9" t="n"/>
-      <c r="I22" s="58">
+      <c r="I22" s="62">
         <f>H22*F22</f>
         <v/>
       </c>
       <c r="J22" s="18" t="n"/>
-      <c r="K22" s="19" t="n"/>
+      <c r="K22" s="26" t="n"/>
       <c r="L22" s="22" t="n"/>
       <c r="M22" s="18" t="n"/>
       <c r="N22" s="18" t="n"/>
       <c r="O22" s="19" t="n"/>
       <c r="P22" s="53" t="n"/>
       <c r="Q22" s="8" t="n"/>
-      <c r="R22" s="63" t="n"/>
-      <c r="S22" s="64" t="n"/>
-      <c r="T22" s="58">
+      <c r="R22" s="69" t="n"/>
+      <c r="S22" s="70" t="n"/>
+      <c r="T22" s="62">
         <f>S22*Q22</f>
         <v/>
       </c>
       <c r="U22" s="18" t="n"/>
-      <c r="V22" s="19" t="n"/>
+      <c r="V22" s="26" t="n"/>
     </row>
     <row r="23" ht="20.1" customHeight="1" s="50">
       <c r="A23" s="22" t="n"/>
@@ -3492,26 +3533,26 @@
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="9" t="n"/>
-      <c r="I23" s="58">
+      <c r="I23" s="62">
         <f>H23*F23</f>
         <v/>
       </c>
       <c r="J23" s="18" t="n"/>
-      <c r="K23" s="19" t="n"/>
+      <c r="K23" s="26" t="n"/>
       <c r="L23" s="22" t="n"/>
       <c r="M23" s="18" t="n"/>
       <c r="N23" s="18" t="n"/>
       <c r="O23" s="19" t="n"/>
       <c r="P23" s="53" t="n"/>
       <c r="Q23" s="8" t="n"/>
-      <c r="R23" s="63" t="n"/>
-      <c r="S23" s="64" t="n"/>
-      <c r="T23" s="58">
+      <c r="R23" s="69" t="n"/>
+      <c r="S23" s="70" t="n"/>
+      <c r="T23" s="62">
         <f>S23*Q23</f>
         <v/>
       </c>
       <c r="U23" s="18" t="n"/>
-      <c r="V23" s="19" t="n"/>
+      <c r="V23" s="26" t="n"/>
     </row>
     <row r="24" ht="20.1" customHeight="1" s="50">
       <c r="A24" s="22" t="n"/>
@@ -3522,26 +3563,26 @@
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="9" t="n"/>
-      <c r="I24" s="58">
+      <c r="I24" s="62">
         <f>H24*F24</f>
         <v/>
       </c>
       <c r="J24" s="18" t="n"/>
-      <c r="K24" s="19" t="n"/>
+      <c r="K24" s="26" t="n"/>
       <c r="L24" s="22" t="n"/>
       <c r="M24" s="18" t="n"/>
       <c r="N24" s="18" t="n"/>
       <c r="O24" s="19" t="n"/>
       <c r="P24" s="53" t="n"/>
       <c r="Q24" s="8" t="n"/>
-      <c r="R24" s="63" t="n"/>
-      <c r="S24" s="64" t="n"/>
-      <c r="T24" s="58">
+      <c r="R24" s="69" t="n"/>
+      <c r="S24" s="70" t="n"/>
+      <c r="T24" s="62">
         <f>S24*Q24</f>
         <v/>
       </c>
       <c r="U24" s="18" t="n"/>
-      <c r="V24" s="19" t="n"/>
+      <c r="V24" s="26" t="n"/>
     </row>
     <row r="25" ht="20.1" customHeight="1" s="50">
       <c r="A25" s="22" t="n"/>
@@ -3552,26 +3593,26 @@
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="9" t="n"/>
-      <c r="I25" s="58">
+      <c r="I25" s="62">
         <f>H25*F25</f>
         <v/>
       </c>
       <c r="J25" s="18" t="n"/>
-      <c r="K25" s="19" t="n"/>
+      <c r="K25" s="26" t="n"/>
       <c r="L25" s="22" t="n"/>
       <c r="M25" s="18" t="n"/>
       <c r="N25" s="18" t="n"/>
       <c r="O25" s="19" t="n"/>
       <c r="P25" s="53" t="n"/>
       <c r="Q25" s="8" t="n"/>
-      <c r="R25" s="63" t="n"/>
-      <c r="S25" s="64" t="n"/>
-      <c r="T25" s="58">
+      <c r="R25" s="69" t="n"/>
+      <c r="S25" s="70" t="n"/>
+      <c r="T25" s="62">
         <f>S25*Q25</f>
         <v/>
       </c>
       <c r="U25" s="18" t="n"/>
-      <c r="V25" s="19" t="n"/>
+      <c r="V25" s="26" t="n"/>
     </row>
     <row r="26" ht="20.1" customHeight="1" s="50">
       <c r="A26" s="22" t="n"/>
@@ -3582,26 +3623,26 @@
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="9" t="n"/>
-      <c r="I26" s="58">
+      <c r="I26" s="62">
         <f>H26*F26</f>
         <v/>
       </c>
       <c r="J26" s="18" t="n"/>
-      <c r="K26" s="19" t="n"/>
+      <c r="K26" s="26" t="n"/>
       <c r="L26" s="22" t="n"/>
       <c r="M26" s="18" t="n"/>
       <c r="N26" s="18" t="n"/>
       <c r="O26" s="19" t="n"/>
       <c r="P26" s="53" t="n"/>
       <c r="Q26" s="8" t="n"/>
-      <c r="R26" s="63" t="n"/>
-      <c r="S26" s="64" t="n"/>
-      <c r="T26" s="58">
+      <c r="R26" s="69" t="n"/>
+      <c r="S26" s="70" t="n"/>
+      <c r="T26" s="62">
         <f>S26*Q26</f>
         <v/>
       </c>
       <c r="U26" s="18" t="n"/>
-      <c r="V26" s="19" t="n"/>
+      <c r="V26" s="26" t="n"/>
     </row>
     <row r="27" ht="20.1" customHeight="1" s="50">
       <c r="A27" s="22" t="n"/>
@@ -3612,26 +3653,26 @@
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
       <c r="H27" s="9" t="n"/>
-      <c r="I27" s="58">
+      <c r="I27" s="62">
         <f>H27*F27</f>
         <v/>
       </c>
       <c r="J27" s="18" t="n"/>
-      <c r="K27" s="19" t="n"/>
+      <c r="K27" s="26" t="n"/>
       <c r="L27" s="22" t="n"/>
       <c r="M27" s="18" t="n"/>
       <c r="N27" s="18" t="n"/>
       <c r="O27" s="19" t="n"/>
       <c r="P27" s="53" t="n"/>
       <c r="Q27" s="8" t="n"/>
-      <c r="R27" s="63" t="n"/>
-      <c r="S27" s="64" t="n"/>
-      <c r="T27" s="58">
+      <c r="R27" s="69" t="n"/>
+      <c r="S27" s="70" t="n"/>
+      <c r="T27" s="62">
         <f>S27*Q27</f>
         <v/>
       </c>
       <c r="U27" s="18" t="n"/>
-      <c r="V27" s="19" t="n"/>
+      <c r="V27" s="26" t="n"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" s="50">
       <c r="A28" s="22" t="n"/>
@@ -3642,26 +3683,26 @@
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
       <c r="H28" s="9" t="n"/>
-      <c r="I28" s="58">
+      <c r="I28" s="62">
         <f>H28*F28</f>
         <v/>
       </c>
       <c r="J28" s="18" t="n"/>
-      <c r="K28" s="19" t="n"/>
+      <c r="K28" s="26" t="n"/>
       <c r="L28" s="22" t="n"/>
       <c r="M28" s="18" t="n"/>
       <c r="N28" s="18" t="n"/>
       <c r="O28" s="19" t="n"/>
       <c r="P28" s="53" t="n"/>
       <c r="Q28" s="8" t="n"/>
-      <c r="R28" s="63" t="n"/>
-      <c r="S28" s="64" t="n"/>
-      <c r="T28" s="58">
+      <c r="R28" s="69" t="n"/>
+      <c r="S28" s="70" t="n"/>
+      <c r="T28" s="62">
         <f>S28*Q28</f>
         <v/>
       </c>
       <c r="U28" s="18" t="n"/>
-      <c r="V28" s="19" t="n"/>
+      <c r="V28" s="26" t="n"/>
     </row>
     <row r="29" ht="20.1" customHeight="1" s="50">
       <c r="A29" s="22" t="n"/>
@@ -3672,26 +3713,26 @@
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
       <c r="H29" s="10" t="n"/>
-      <c r="I29" s="58">
+      <c r="I29" s="62">
         <f>H29*F29</f>
         <v/>
       </c>
       <c r="J29" s="18" t="n"/>
-      <c r="K29" s="19" t="n"/>
+      <c r="K29" s="26" t="n"/>
       <c r="L29" s="22" t="n"/>
       <c r="M29" s="18" t="n"/>
       <c r="N29" s="18" t="n"/>
       <c r="O29" s="19" t="n"/>
       <c r="P29" s="53" t="n"/>
       <c r="Q29" s="8" t="n"/>
-      <c r="R29" s="63" t="n"/>
-      <c r="S29" s="65" t="n"/>
-      <c r="T29" s="58">
+      <c r="R29" s="69" t="n"/>
+      <c r="S29" s="71" t="n"/>
+      <c r="T29" s="62">
         <f>S29*Q29</f>
         <v/>
       </c>
       <c r="U29" s="18" t="n"/>
-      <c r="V29" s="19" t="n"/>
+      <c r="V29" s="26" t="n"/>
     </row>
     <row r="30" ht="20.1" customHeight="1" s="50">
       <c r="A30" s="22" t="n"/>
@@ -3702,26 +3743,26 @@
       <c r="F30" s="11" t="n"/>
       <c r="G30" s="11" t="n"/>
       <c r="H30" s="10" t="n"/>
-      <c r="I30" s="58">
+      <c r="I30" s="62">
         <f>H30*F30</f>
         <v/>
       </c>
       <c r="J30" s="18" t="n"/>
-      <c r="K30" s="19" t="n"/>
+      <c r="K30" s="26" t="n"/>
       <c r="L30" s="22" t="n"/>
       <c r="M30" s="18" t="n"/>
       <c r="N30" s="18" t="n"/>
       <c r="O30" s="19" t="n"/>
       <c r="P30" s="55" t="n"/>
       <c r="Q30" s="11" t="n"/>
-      <c r="R30" s="66" t="n"/>
-      <c r="S30" s="65" t="n"/>
-      <c r="T30" s="58">
+      <c r="R30" s="72" t="n"/>
+      <c r="S30" s="71" t="n"/>
+      <c r="T30" s="62">
         <f>S30*Q30</f>
         <v/>
       </c>
       <c r="U30" s="18" t="n"/>
-      <c r="V30" s="19" t="n"/>
+      <c r="V30" s="26" t="n"/>
     </row>
     <row r="31" ht="20.1" customHeight="1" s="50">
       <c r="A31" s="22" t="n"/>
@@ -3732,26 +3773,26 @@
       <c r="F31" s="11" t="n"/>
       <c r="G31" s="11" t="n"/>
       <c r="H31" s="10" t="n"/>
-      <c r="I31" s="58">
+      <c r="I31" s="62">
         <f>H31*F31</f>
         <v/>
       </c>
       <c r="J31" s="18" t="n"/>
-      <c r="K31" s="19" t="n"/>
+      <c r="K31" s="26" t="n"/>
       <c r="L31" s="22" t="n"/>
       <c r="M31" s="18" t="n"/>
       <c r="N31" s="18" t="n"/>
       <c r="O31" s="19" t="n"/>
       <c r="P31" s="55" t="n"/>
       <c r="Q31" s="11" t="n"/>
-      <c r="R31" s="66" t="n"/>
-      <c r="S31" s="65" t="n"/>
-      <c r="T31" s="58">
+      <c r="R31" s="72" t="n"/>
+      <c r="S31" s="71" t="n"/>
+      <c r="T31" s="62">
         <f>S31*Q31</f>
         <v/>
       </c>
       <c r="U31" s="18" t="n"/>
-      <c r="V31" s="19" t="n"/>
+      <c r="V31" s="26" t="n"/>
     </row>
     <row r="32" ht="20.1" customHeight="1" s="50">
       <c r="A32" s="47" t="n"/>
@@ -3762,26 +3803,26 @@
       <c r="F32" s="11" t="n"/>
       <c r="G32" s="11" t="n"/>
       <c r="H32" s="11" t="n"/>
-      <c r="I32" s="58">
+      <c r="I32" s="62">
         <f>H32*F32</f>
         <v/>
       </c>
       <c r="J32" s="18" t="n"/>
-      <c r="K32" s="19" t="n"/>
+      <c r="K32" s="26" t="n"/>
       <c r="L32" s="24" t="n"/>
       <c r="M32" s="18" t="n"/>
       <c r="N32" s="18" t="n"/>
       <c r="O32" s="19" t="n"/>
       <c r="P32" s="55" t="n"/>
       <c r="Q32" s="11" t="n"/>
-      <c r="R32" s="66" t="n"/>
-      <c r="S32" s="66" t="n"/>
-      <c r="T32" s="58">
+      <c r="R32" s="72" t="n"/>
+      <c r="S32" s="72" t="n"/>
+      <c r="T32" s="62">
         <f>S32*Q32</f>
         <v/>
       </c>
       <c r="U32" s="18" t="n"/>
-      <c r="V32" s="19" t="n"/>
+      <c r="V32" s="26" t="n"/>
     </row>
     <row r="33" ht="20.1" customHeight="1" s="50">
       <c r="A33" s="36" t="inlineStr">
@@ -3796,26 +3837,26 @@
       <c r="F33" s="18" t="n"/>
       <c r="G33" s="18" t="n"/>
       <c r="H33" s="19" t="n"/>
-      <c r="I33" s="58">
+      <c r="I33" s="62">
         <f>I17</f>
         <v/>
       </c>
       <c r="J33" s="18" t="n"/>
-      <c r="K33" s="19" t="n"/>
+      <c r="K33" s="26" t="n"/>
       <c r="L33" s="22" t="n"/>
       <c r="M33" s="18" t="n"/>
       <c r="N33" s="18" t="n"/>
       <c r="O33" s="19" t="n"/>
       <c r="P33" s="55" t="n"/>
       <c r="Q33" s="11" t="n"/>
-      <c r="R33" s="66" t="n"/>
-      <c r="S33" s="65" t="n"/>
-      <c r="T33" s="58">
+      <c r="R33" s="72" t="n"/>
+      <c r="S33" s="71" t="n"/>
+      <c r="T33" s="62">
         <f>S33*Q33</f>
         <v/>
       </c>
       <c r="U33" s="18" t="n"/>
-      <c r="V33" s="19" t="n"/>
+      <c r="V33" s="26" t="n"/>
     </row>
     <row r="34" ht="20.1" customHeight="1" s="50">
       <c r="A34" s="36" t="inlineStr">
@@ -3830,26 +3871,26 @@
       <c r="F34" s="18" t="n"/>
       <c r="G34" s="18" t="n"/>
       <c r="H34" s="19" t="n"/>
-      <c r="I34" s="59">
+      <c r="I34" s="67">
         <f>I33*10%</f>
         <v/>
       </c>
       <c r="J34" s="18" t="n"/>
-      <c r="K34" s="19" t="n"/>
+      <c r="K34" s="26" t="n"/>
       <c r="L34" s="24" t="n"/>
       <c r="M34" s="18" t="n"/>
       <c r="N34" s="18" t="n"/>
       <c r="O34" s="19" t="n"/>
       <c r="P34" s="55" t="n"/>
       <c r="Q34" s="11" t="n"/>
-      <c r="R34" s="66" t="n"/>
-      <c r="S34" s="66" t="n"/>
-      <c r="T34" s="58">
+      <c r="R34" s="72" t="n"/>
+      <c r="S34" s="72" t="n"/>
+      <c r="T34" s="62">
         <f>S34*Q34</f>
         <v/>
       </c>
       <c r="U34" s="18" t="n"/>
-      <c r="V34" s="19" t="n"/>
+      <c r="V34" s="26" t="n"/>
     </row>
     <row r="35" ht="20.1" customHeight="1" s="50" thickBot="1">
       <c r="A35" s="38" t="inlineStr">
@@ -3864,7 +3905,7 @@
       <c r="F35" s="30" t="n"/>
       <c r="G35" s="30" t="n"/>
       <c r="H35" s="39" t="n"/>
-      <c r="I35" s="60">
+      <c r="I35" s="29">
         <f>I33+I34</f>
         <v/>
       </c>
@@ -3882,12 +3923,12 @@
       <c r="Q35" s="18" t="n"/>
       <c r="R35" s="18" t="n"/>
       <c r="S35" s="19" t="n"/>
-      <c r="T35" s="58">
+      <c r="T35" s="62">
         <f>SUM(T17:V34)</f>
         <v/>
       </c>
       <c r="U35" s="18" t="n"/>
-      <c r="V35" s="19" t="n"/>
+      <c r="V35" s="26" t="n"/>
     </row>
     <row r="36" ht="20.1" customHeight="1" s="50">
       <c r="A36" s="49" t="inlineStr">
@@ -3907,12 +3948,12 @@
       <c r="Q36" s="18" t="n"/>
       <c r="R36" s="18" t="n"/>
       <c r="S36" s="19" t="n"/>
-      <c r="T36" s="59">
+      <c r="T36" s="67">
         <f>T35*10%</f>
         <v/>
       </c>
       <c r="U36" s="18" t="n"/>
-      <c r="V36" s="19" t="n"/>
+      <c r="V36" s="26" t="n"/>
     </row>
     <row r="37" ht="20.1" customHeight="1" s="50" thickBot="1">
       <c r="L37" s="38" t="inlineStr">
@@ -3927,7 +3968,7 @@
       <c r="Q37" s="30" t="n"/>
       <c r="R37" s="30" t="n"/>
       <c r="S37" s="39" t="n"/>
-      <c r="T37" s="60">
+      <c r="T37" s="29">
         <f>T35+T36</f>
         <v/>
       </c>
